--- a/public/crawlability-blender.global-september-2026.xlsx
+++ b/public/crawlability-blender.global-september-2026.xlsx
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -478,27 +478,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להעמיד קובץ robots.txt תקין שמחזיר 200 ומכיל שורת Sitemap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>להעמיד מפת אתר XML נגישה ולהצהיר עליה ב-robots.txt וב-Search Console.</t>
+          <t>להעמיד robots.txt פשוט (User-agent: * / Allow: /) ולהוסיף canonical לעמוד הבית.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-blender.global-september-2026.xlsx
+++ b/public/crawlability-blender.global-september-2026.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להעמיד robots.txt פשוט (User-agent: * / Allow: /) ולהוסיף canonical לעמוד הבית.</t>
+          <t>להעמיד robots.txt פשוט (User-agent: * / Allow: /).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>להוסיף תגית canonical לעמוד הבית (ולעמודי האתר).</t>
         </is>
       </c>
     </row>
